--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V434"/>
+  <dimension ref="A1:V441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41884,10 +41884,8 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
+      <c r="A421" t="n">
+        <v>1119</v>
       </c>
       <c r="B421" t="inlineStr">
         <is>
@@ -41941,7 +41939,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N421" s="2" t="n">
+      <c r="N421" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O421" t="inlineStr">
@@ -41986,10 +41984,8 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A422" t="n">
+        <v>1218</v>
       </c>
       <c r="B422" t="inlineStr">
         <is>
@@ -42041,7 +42037,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N422" s="2" t="n">
+      <c r="N422" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O422" t="inlineStr">
@@ -42086,10 +42082,8 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A423" t="n">
+        <v>1218</v>
       </c>
       <c r="B423" t="inlineStr">
         <is>
@@ -42141,7 +42135,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N423" s="2" t="n">
+      <c r="N423" s="1" t="n">
         <v>42801</v>
       </c>
       <c r="O423" t="inlineStr">
@@ -42186,10 +42180,8 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A424" t="n">
+        <v>1218</v>
       </c>
       <c r="B424" t="inlineStr">
         <is>
@@ -42241,7 +42233,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N424" s="2" t="n">
+      <c r="N424" s="1" t="n">
         <v>42801</v>
       </c>
       <c r="O424" t="inlineStr">
@@ -42286,10 +42278,8 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A425" t="n">
+        <v>1218</v>
       </c>
       <c r="B425" t="inlineStr">
         <is>
@@ -42341,7 +42331,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N425" s="2" t="n">
+      <c r="N425" s="1" t="n">
         <v>40605</v>
       </c>
       <c r="O425" t="inlineStr">
@@ -42386,10 +42376,8 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>1704</t>
-        </is>
+      <c r="A426" t="n">
+        <v>1704</v>
       </c>
       <c r="B426" t="inlineStr">
         <is>
@@ -42443,7 +42431,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N426" s="2" t="n">
+      <c r="N426" s="1" t="n">
         <v>41254</v>
       </c>
       <c r="O426" t="inlineStr">
@@ -42488,10 +42476,8 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A427" t="n">
+        <v>1716</v>
       </c>
       <c r="B427" t="inlineStr">
         <is>
@@ -42543,7 +42529,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N427" s="2" t="n">
+      <c r="N427" s="1" t="n">
         <v>43412</v>
       </c>
       <c r="O427" t="inlineStr">
@@ -42588,10 +42574,8 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A428" t="n">
+        <v>1722</v>
       </c>
       <c r="B428" t="inlineStr">
         <is>
@@ -42643,7 +42627,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N428" s="2" t="n">
+      <c r="N428" s="1" t="n">
         <v>39553</v>
       </c>
       <c r="O428" t="inlineStr">
@@ -42688,10 +42672,8 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A429" t="n">
+        <v>1828</v>
       </c>
       <c r="B429" t="inlineStr">
         <is>
@@ -42743,7 +42725,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N429" s="2" t="n">
+      <c r="N429" s="1" t="n">
         <v>40942</v>
       </c>
       <c r="O429" t="inlineStr">
@@ -42788,10 +42770,8 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
+      <c r="A430" t="n">
+        <v>2702</v>
       </c>
       <c r="B430" t="inlineStr">
         <is>
@@ -42845,7 +42825,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N430" s="2" t="n">
+      <c r="N430" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O430" t="inlineStr">
@@ -42890,10 +42870,8 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A431" t="n">
+        <v>2728</v>
       </c>
       <c r="B431" t="inlineStr">
         <is>
@@ -42945,7 +42923,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N431" s="2" t="n">
+      <c r="N431" s="1" t="n">
         <v>42416</v>
       </c>
       <c r="O431" t="inlineStr">
@@ -42990,10 +42968,8 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A432" t="n">
+        <v>2728</v>
       </c>
       <c r="B432" t="inlineStr">
         <is>
@@ -43045,7 +43021,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N432" s="2" t="n">
+      <c r="N432" s="1" t="n">
         <v>36262</v>
       </c>
       <c r="O432" t="inlineStr">
@@ -43090,10 +43066,8 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A433" t="n">
+        <v>2728</v>
       </c>
       <c r="B433" t="inlineStr">
         <is>
@@ -43145,7 +43119,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N433" s="2" t="n">
+      <c r="N433" s="1" t="n">
         <v>42412</v>
       </c>
       <c r="O433" t="inlineStr">
@@ -43190,10 +43164,8 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A434" t="n">
+        <v>2728</v>
       </c>
       <c r="B434" t="inlineStr">
         <is>
@@ -43245,7 +43217,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N434" s="2" t="n">
+      <c r="N434" s="1" t="n">
         <v>41459</v>
       </c>
       <c r="O434" t="inlineStr">
@@ -43286,6 +43258,714 @@
       <c r="V434" t="inlineStr">
         <is>
           <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL MAGDALENA - UNIMAGDALENA</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F435" t="n">
+        <v>106632</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN PSICOLOGÍA CLÍNICA, JURÍDICA Y FORENSE</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I435" t="n">
+        <v>50</v>
+      </c>
+      <c r="J435" t="n">
+        <v>4</v>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L435" t="n">
+        <v>10146810</v>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N435" s="2" t="n">
+        <v>43098</v>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T435" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA GUAJIRA</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F436" t="n">
+        <v>54837</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN MEDICINA TROPICAL</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I436" t="n">
+        <v>93</v>
+      </c>
+      <c r="J436" t="n">
+        <v>8</v>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
+      <c r="N436" s="2" t="n">
+        <v>39996</v>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T436" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F437" t="n">
+        <v>108535</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN COMUNICACIÓN Y PERIODISMO CON INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I437" t="n">
+        <v>24</v>
+      </c>
+      <c r="J437" t="n">
+        <v>2</v>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L437" t="n">
+        <v>6802000</v>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N437" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T437" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2713</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA LOS LIBERTADORES</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F438" t="n">
+        <v>109101</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DERECHOS HUMANOS Y JUSTICIA TRANSICIONAL</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I438" t="n">
+        <v>48</v>
+      </c>
+      <c r="J438" t="n">
+        <v>4</v>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L438" t="n">
+        <v>6955500</v>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N438" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T438" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>POLITECNICO GRANCOLOMBIANO</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F439" t="n">
+        <v>105212</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I439" t="n">
+        <v>53</v>
+      </c>
+      <c r="J439" t="n">
+        <v>4</v>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L439" t="n">
+        <v>9512000</v>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N439" s="2" t="n">
+        <v>45118</v>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2831</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE CIENCIA Y DESARROLLO - UNICIENCIA</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F440" t="n">
+        <v>108200</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DERECHO CONSTITUCIONAL</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I440" t="n">
+        <v>22</v>
+      </c>
+      <c r="J440" t="n">
+        <v>1</v>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L440" t="n">
+        <v>14000000</v>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N440" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T440" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2841</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Bello</t>
+        </is>
+      </c>
+      <c r="F441" t="n">
+        <v>111292</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN TECNOLÓGICA EN HERRAMIENTAS PARA LA GESTIÓN DE DATOS - BIG DATA</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I441" t="n">
+        <v>24</v>
+      </c>
+      <c r="J441" t="n">
+        <v>2</v>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L441" t="n">
+        <v>5629100</v>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N441" s="2" t="n">
+        <v>44809</v>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>Especialización tecnológica</t>
+        </is>
+      </c>
+      <c r="T441" t="inlineStr">
+        <is>
+          <t>08/09/2026</t>
+        </is>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V441"/>
+  <dimension ref="A1:V461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43262,10 +43262,8 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
+      <c r="A435" t="n">
+        <v>1213</v>
       </c>
       <c r="B435" t="inlineStr">
         <is>
@@ -43319,7 +43317,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N435" s="2" t="n">
+      <c r="N435" s="1" t="n">
         <v>43098</v>
       </c>
       <c r="O435" t="inlineStr">
@@ -43364,10 +43362,8 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A436" t="n">
+        <v>1218</v>
       </c>
       <c r="B436" t="inlineStr">
         <is>
@@ -43415,7 +43411,7 @@
       </c>
       <c r="L436" t="inlineStr"/>
       <c r="M436" t="inlineStr"/>
-      <c r="N436" s="2" t="n">
+      <c r="N436" s="1" t="n">
         <v>39996</v>
       </c>
       <c r="O436" t="inlineStr">
@@ -43460,10 +43456,8 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="A437" t="n">
+        <v>1830</v>
       </c>
       <c r="B437" t="inlineStr">
         <is>
@@ -43517,7 +43511,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N437" s="2" t="n">
+      <c r="N437" s="1" t="n">
         <v>46154</v>
       </c>
       <c r="O437" t="inlineStr">
@@ -43562,10 +43556,8 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>2713</t>
-        </is>
+      <c r="A438" t="n">
+        <v>2713</v>
       </c>
       <c r="B438" t="inlineStr">
         <is>
@@ -43619,7 +43611,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N438" s="2" t="n">
+      <c r="N438" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O438" t="inlineStr">
@@ -43664,10 +43656,8 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
+      <c r="A439" t="n">
+        <v>2725</v>
       </c>
       <c r="B439" t="inlineStr">
         <is>
@@ -43721,7 +43711,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N439" s="2" t="n">
+      <c r="N439" s="1" t="n">
         <v>45118</v>
       </c>
       <c r="O439" t="inlineStr">
@@ -43766,10 +43756,8 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="inlineStr">
-        <is>
-          <t>2831</t>
-        </is>
+      <c r="A440" t="n">
+        <v>2831</v>
       </c>
       <c r="B440" t="inlineStr">
         <is>
@@ -43823,7 +43811,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N440" s="2" t="n">
+      <c r="N440" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O440" t="inlineStr">
@@ -43868,10 +43856,8 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>2841</t>
-        </is>
+      <c r="A441" t="n">
+        <v>2841</v>
       </c>
       <c r="B441" t="inlineStr">
         <is>
@@ -43925,7 +43911,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N441" s="2" t="n">
+      <c r="N441" s="1" t="n">
         <v>44809</v>
       </c>
       <c r="O441" t="inlineStr">
@@ -43966,6 +43952,2010 @@
       <c r="V441" t="inlineStr">
         <is>
           <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD MILITAR-NUEVA GRANADA</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F442" t="n">
+        <v>391</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN CIRUGIA PLASTICA RECONSTRUTIVA Y ESTETICA</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I442" t="n">
+        <v>294</v>
+      </c>
+      <c r="J442" t="n">
+        <v>4</v>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L442" t="n">
+        <v>41831000</v>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N442" s="2" t="n">
+        <v>35875</v>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T442" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE BOGOTA - JORGE TADEO LOZANO</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F443" t="n">
+        <v>104658</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DESARROLLO DE BASES DE DATOS</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I443" t="n">
+        <v>24</v>
+      </c>
+      <c r="J443" t="n">
+        <v>2</v>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N443" s="2" t="n">
+        <v>42192</v>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T443" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE BOGOTA - JORGE TADEO LOZANO</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F444" t="n">
+        <v>103120</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN EVALUACIÓN DEL IMPACTO AMBIENTAL DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I444" t="n">
+        <v>28</v>
+      </c>
+      <c r="J444" t="n">
+        <v>2</v>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N444" s="2" t="n">
+        <v>41697</v>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr">
+        <is>
+          <t>Geología, otros programas de ciencias naturales</t>
+        </is>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T444" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE BOGOTA - JORGE TADEO LOZANO</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F445" t="n">
+        <v>103907</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN DE LA SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I445" t="n">
+        <v>27</v>
+      </c>
+      <c r="J445" t="n">
+        <v>2</v>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N445" s="2" t="n">
+        <v>41978</v>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T445" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F446" t="n">
+        <v>107412</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA PARA INGENIEROS</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I446" t="n">
+        <v>26</v>
+      </c>
+      <c r="J446" t="n">
+        <v>2</v>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N446" s="2" t="n">
+        <v>43363</v>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T446" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V446" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F447" t="n">
+        <v>1993</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO COMERCIAL</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I447" t="n">
+        <v>31</v>
+      </c>
+      <c r="J447" t="n">
+        <v>1</v>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N447" s="2" t="n">
+        <v>35885</v>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T447" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F448" t="n">
+        <v>103351</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I448" t="n">
+        <v>31</v>
+      </c>
+      <c r="J448" t="n">
+        <v>2</v>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N448" s="2" t="n">
+        <v>41800</v>
+      </c>
+      <c r="O448" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T448" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F449" t="n">
+        <v>103349</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO PENAL</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I449" t="n">
+        <v>31</v>
+      </c>
+      <c r="J449" t="n">
+        <v>2</v>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N449" s="2" t="n">
+        <v>41799</v>
+      </c>
+      <c r="O449" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T449" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F450" t="n">
+        <v>104920</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO TRIBUTARIO</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I450" t="n">
+        <v>31</v>
+      </c>
+      <c r="J450" t="n">
+        <v>2</v>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N450" s="2" t="n">
+        <v>42275</v>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F451" t="n">
+        <v>1995</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GERENCIA TRIBUTARIA</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I451" t="n">
+        <v>26</v>
+      </c>
+      <c r="J451" t="n">
+        <v>6</v>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N451" s="2" t="n">
+        <v>35885</v>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F452" t="n">
+        <v>91093</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN HEMATOLOGÍA Y ONCOLOGÍA CLÍNICA</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I452" t="n">
+        <v>205</v>
+      </c>
+      <c r="J452" t="n">
+        <v>3</v>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L452" t="n">
+        <v>17419968</v>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N452" s="2" t="n">
+        <v>40609</v>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>Especialización médico quirúrgica</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F453" t="n">
+        <v>104651</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN LEGISLACIÓN LABORAL Y DE LA SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I453" t="n">
+        <v>27</v>
+      </c>
+      <c r="J453" t="n">
+        <v>2</v>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N453" s="2" t="n">
+        <v>42178</v>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F454" t="n">
+        <v>104919</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN LEGISLACIÓN TRIBUTARIA</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I454" t="n">
+        <v>31</v>
+      </c>
+      <c r="J454" t="n">
+        <v>2</v>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N454" s="2" t="n">
+        <v>42275</v>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V454" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F455" t="n">
+        <v>104271</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN ADMINISTRACIÓN</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I455" t="n">
+        <v>52</v>
+      </c>
+      <c r="J455" t="n">
+        <v>4</v>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N455" s="2" t="n">
+        <v>42069</v>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F456" t="n">
+        <v>105684</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CONTABILIDAD Y TRIBUTACIÓN</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I456" t="n">
+        <v>50</v>
+      </c>
+      <c r="J456" t="n">
+        <v>4</v>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N456" s="2" t="n">
+        <v>42552</v>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F457" t="n">
+        <v>103667</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN FORMULACIÓN DE PRODUCTOS QUÍMICOS Y DERIVADOS</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I457" t="n">
+        <v>50</v>
+      </c>
+      <c r="J457" t="n">
+        <v>4</v>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N457" s="2" t="n">
+        <v>41888</v>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>Ciencias físicas</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>Química</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr">
+        <is>
+          <t>Química y afines</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F458" t="n">
+        <v>102592</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN PERIODISMO</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I458" t="n">
+        <v>51</v>
+      </c>
+      <c r="J458" t="n">
+        <v>4</v>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N458" s="2" t="n">
+        <v>41452</v>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F459" t="n">
+        <v>102701</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO ADMINISTRATIVO LABORAL</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I459" t="n">
+        <v>26</v>
+      </c>
+      <c r="J459" t="n">
+        <v>2</v>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N459" s="2" t="n">
+        <v>41488</v>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V459" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F460" t="n">
+        <v>102700</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN RESPONSABILIDAD ESTATAL</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I460" t="n">
+        <v>26</v>
+      </c>
+      <c r="J460" t="n">
+        <v>2</v>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N460" s="2" t="n">
+        <v>41488</v>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V460" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2745</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA COMPENSAR</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F461" t="n">
+        <v>106063</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INNOVACIÓN EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I461" t="n">
+        <v>21</v>
+      </c>
+      <c r="J461" t="n">
+        <v>2</v>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N461" s="2" t="n">
+        <v>42723</v>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>15/09/2026</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V461"/>
+  <dimension ref="A1:V481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43956,10 +43956,8 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
+      <c r="A442" t="n">
+        <v>1117</v>
       </c>
       <c r="B442" t="inlineStr">
         <is>
@@ -44013,7 +44011,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N442" s="2" t="n">
+      <c r="N442" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O442" t="inlineStr">
@@ -44058,10 +44056,8 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
+      <c r="A443" t="n">
+        <v>1707</v>
       </c>
       <c r="B443" t="inlineStr">
         <is>
@@ -44113,7 +44109,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N443" s="2" t="n">
+      <c r="N443" s="1" t="n">
         <v>42192</v>
       </c>
       <c r="O443" t="inlineStr">
@@ -44158,10 +44154,8 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
+      <c r="A444" t="n">
+        <v>1707</v>
       </c>
       <c r="B444" t="inlineStr">
         <is>
@@ -44213,7 +44207,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N444" s="2" t="n">
+      <c r="N444" s="1" t="n">
         <v>41697</v>
       </c>
       <c r="O444" t="inlineStr">
@@ -44258,10 +44252,8 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
+      <c r="A445" t="n">
+        <v>1707</v>
       </c>
       <c r="B445" t="inlineStr">
         <is>
@@ -44313,7 +44305,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N445" s="2" t="n">
+      <c r="N445" s="1" t="n">
         <v>41978</v>
       </c>
       <c r="O445" t="inlineStr">
@@ -44358,10 +44350,8 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A446" t="n">
+        <v>1710</v>
       </c>
       <c r="B446" t="inlineStr">
         <is>
@@ -44413,7 +44403,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N446" s="2" t="n">
+      <c r="N446" s="1" t="n">
         <v>43363</v>
       </c>
       <c r="O446" t="inlineStr">
@@ -44458,10 +44448,8 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A447" t="n">
+        <v>1828</v>
       </c>
       <c r="B447" t="inlineStr">
         <is>
@@ -44513,7 +44501,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N447" s="2" t="n">
+      <c r="N447" s="1" t="n">
         <v>35885</v>
       </c>
       <c r="O447" t="inlineStr">
@@ -44558,10 +44546,8 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A448" t="n">
+        <v>1828</v>
       </c>
       <c r="B448" t="inlineStr">
         <is>
@@ -44613,7 +44599,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N448" s="2" t="n">
+      <c r="N448" s="1" t="n">
         <v>41800</v>
       </c>
       <c r="O448" t="inlineStr">
@@ -44658,10 +44644,8 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A449" t="n">
+        <v>1828</v>
       </c>
       <c r="B449" t="inlineStr">
         <is>
@@ -44713,7 +44697,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N449" s="2" t="n">
+      <c r="N449" s="1" t="n">
         <v>41799</v>
       </c>
       <c r="O449" t="inlineStr">
@@ -44758,10 +44742,8 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A450" t="n">
+        <v>1828</v>
       </c>
       <c r="B450" t="inlineStr">
         <is>
@@ -44813,7 +44795,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N450" s="2" t="n">
+      <c r="N450" s="1" t="n">
         <v>42275</v>
       </c>
       <c r="O450" t="inlineStr">
@@ -44858,10 +44840,8 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A451" t="n">
+        <v>1828</v>
       </c>
       <c r="B451" t="inlineStr">
         <is>
@@ -44913,7 +44893,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N451" s="2" t="n">
+      <c r="N451" s="1" t="n">
         <v>35885</v>
       </c>
       <c r="O451" t="inlineStr">
@@ -44958,10 +44938,8 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A452" t="n">
+        <v>1828</v>
       </c>
       <c r="B452" t="inlineStr">
         <is>
@@ -45015,7 +44993,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N452" s="2" t="n">
+      <c r="N452" s="1" t="n">
         <v>40609</v>
       </c>
       <c r="O452" t="inlineStr">
@@ -45060,10 +45038,8 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A453" t="n">
+        <v>1828</v>
       </c>
       <c r="B453" t="inlineStr">
         <is>
@@ -45115,7 +45091,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N453" s="2" t="n">
+      <c r="N453" s="1" t="n">
         <v>42178</v>
       </c>
       <c r="O453" t="inlineStr">
@@ -45160,10 +45136,8 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A454" t="n">
+        <v>1828</v>
       </c>
       <c r="B454" t="inlineStr">
         <is>
@@ -45215,7 +45189,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N454" s="2" t="n">
+      <c r="N454" s="1" t="n">
         <v>42275</v>
       </c>
       <c r="O454" t="inlineStr">
@@ -45260,10 +45234,8 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A455" t="n">
+        <v>1828</v>
       </c>
       <c r="B455" t="inlineStr">
         <is>
@@ -45315,7 +45287,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N455" s="2" t="n">
+      <c r="N455" s="1" t="n">
         <v>42069</v>
       </c>
       <c r="O455" t="inlineStr">
@@ -45360,10 +45332,8 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A456" t="n">
+        <v>1828</v>
       </c>
       <c r="B456" t="inlineStr">
         <is>
@@ -45415,7 +45385,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N456" s="2" t="n">
+      <c r="N456" s="1" t="n">
         <v>42552</v>
       </c>
       <c r="O456" t="inlineStr">
@@ -45460,10 +45430,8 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A457" t="n">
+        <v>1828</v>
       </c>
       <c r="B457" t="inlineStr">
         <is>
@@ -45515,7 +45483,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N457" s="2" t="n">
+      <c r="N457" s="1" t="n">
         <v>41888</v>
       </c>
       <c r="O457" t="inlineStr">
@@ -45560,10 +45528,8 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A458" t="n">
+        <v>1828</v>
       </c>
       <c r="B458" t="inlineStr">
         <is>
@@ -45615,7 +45581,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N458" s="2" t="n">
+      <c r="N458" s="1" t="n">
         <v>41452</v>
       </c>
       <c r="O458" t="inlineStr">
@@ -45660,10 +45626,8 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
+      <c r="A459" t="n">
+        <v>2302</v>
       </c>
       <c r="B459" t="inlineStr">
         <is>
@@ -45715,7 +45679,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N459" s="2" t="n">
+      <c r="N459" s="1" t="n">
         <v>41488</v>
       </c>
       <c r="O459" t="inlineStr">
@@ -45760,10 +45724,8 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
+      <c r="A460" t="n">
+        <v>2302</v>
       </c>
       <c r="B460" t="inlineStr">
         <is>
@@ -45815,7 +45777,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N460" s="2" t="n">
+      <c r="N460" s="1" t="n">
         <v>41488</v>
       </c>
       <c r="O460" t="inlineStr">
@@ -45860,10 +45822,8 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>2745</t>
-        </is>
+      <c r="A461" t="n">
+        <v>2745</v>
       </c>
       <c r="B461" t="inlineStr">
         <is>
@@ -45915,7 +45875,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N461" s="2" t="n">
+      <c r="N461" s="1" t="n">
         <v>42723</v>
       </c>
       <c r="O461" t="inlineStr">
@@ -45956,6 +45916,2022 @@
       <c r="V461" t="inlineStr">
         <is>
           <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F462" t="n">
+        <v>118957</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN EDUCACION</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I462" t="n">
+        <v>53</v>
+      </c>
+      <c r="J462" t="n">
+        <v>4</v>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N462" s="2" t="n">
+        <v>46184</v>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V462" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F463" t="n">
+        <v>106777</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN COMPORTAMIENTO DEL CONSUMIDOR</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I463" t="n">
+        <v>48</v>
+      </c>
+      <c r="J463" t="n">
+        <v>4</v>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N463" s="2" t="n">
+        <v>43189</v>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F464" t="n">
+        <v>111731</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN DIRECCIÓN DE MARKETING</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I464" t="n">
+        <v>53</v>
+      </c>
+      <c r="J464" t="n">
+        <v>4</v>
+      </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N464" s="2" t="n">
+        <v>45420</v>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V464" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F465" t="n">
+        <v>106776</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN EDUCACIÓN</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I465" t="n">
+        <v>48</v>
+      </c>
+      <c r="J465" t="n">
+        <v>4</v>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N465" s="2" t="n">
+        <v>43189</v>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V465" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F466" t="n">
+        <v>106855</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN ESTUDIOS POLITICOS</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I466" t="n">
+        <v>46</v>
+      </c>
+      <c r="J466" t="n">
+        <v>4</v>
+      </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N466" s="2" t="n">
+        <v>43228</v>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S466" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T466" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U466" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V466" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F467" t="n">
+        <v>17777</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN SEGURIDAD SOCIAL</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I467" t="n">
+        <v>27</v>
+      </c>
+      <c r="J467" t="n">
+        <v>2</v>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N467" s="2" t="n">
+        <v>45146</v>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S467" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T467" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U467" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V467" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F468" t="n">
+        <v>106630</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ANALÍTICA APLICADA A LOS NEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I468" t="n">
+        <v>29</v>
+      </c>
+      <c r="J468" t="n">
+        <v>2</v>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N468" s="2" t="n">
+        <v>43095</v>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S468" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T468" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U468" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V468" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F469" t="n">
+        <v>19936</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN CALIDAD PARA LA COMPETITIVIDAD</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I469" t="n">
+        <v>34</v>
+      </c>
+      <c r="J469" t="n">
+        <v>2</v>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N469" s="2" t="n">
+        <v>43270</v>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S469" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T469" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U469" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V469" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F470" t="n">
+        <v>107265</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ESCRITURAS CREATIVAS</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I470" t="n">
+        <v>32</v>
+      </c>
+      <c r="J470" t="n">
+        <v>2</v>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N470" s="2" t="n">
+        <v>43327</v>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S470" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T470" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U470" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V470" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F471" t="n">
+        <v>107767</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN MERCADEO ESTRATÉGICO EN MEDIOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I471" t="n">
+        <v>22</v>
+      </c>
+      <c r="J471" t="n">
+        <v>2</v>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N471" s="2" t="n">
+        <v>43532</v>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T471" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U471" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V471" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F472" t="n">
+        <v>107579</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN VENTAS</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I472" t="n">
+        <v>21</v>
+      </c>
+      <c r="J472" t="n">
+        <v>2</v>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N472" s="2" t="n">
+        <v>43488</v>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>Ventas al por mayor y al por menor</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T472" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U472" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V472" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F473" t="n">
+        <v>107250</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GERENCIA DE TECNOLOGÍAS DE INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I473" t="n">
+        <v>45</v>
+      </c>
+      <c r="J473" t="n">
+        <v>3</v>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L473" t="n">
+        <v>19469100</v>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N473" s="2" t="n">
+        <v>43326</v>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S473" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T473" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F474" t="n">
+        <v>53031</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PROCESOS DE ALIMENTOS Y BIOMATERIALES</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I474" t="n">
+        <v>25</v>
+      </c>
+      <c r="J474" t="n">
+        <v>3</v>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L474" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N474" s="2" t="n">
+        <v>39308</v>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T474" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U474" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V474" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F475" t="n">
+        <v>104448</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN DESARROLLO ALTERNATIVO, SOSTENIBLE Y SOLIDARIO</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I475" t="n">
+        <v>48</v>
+      </c>
+      <c r="J475" t="n">
+        <v>4</v>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L475" t="n">
+        <v>8214000</v>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N475" s="2" t="n">
+        <v>45182</v>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T475" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V475" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SIMÓN BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F476" t="n">
+        <v>106299</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GESTION DE TECNOLOGIAS DE LA INFORMACION</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I476" t="n">
+        <v>28</v>
+      </c>
+      <c r="J476" t="n">
+        <v>2</v>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L476" t="n">
+        <v>8857881</v>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N476" s="2" t="n">
+        <v>45355</v>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S476" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T476" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2805</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SIMÓN BOLÍVAR</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F477" t="n">
+        <v>105783</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I477" t="n">
+        <v>28</v>
+      </c>
+      <c r="J477" t="n">
+        <v>2</v>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L477" t="n">
+        <v>9226427</v>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N477" s="2" t="n">
+        <v>45037</v>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSIDAD DE LA COSTA CUC</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F478" t="n">
+        <v>106014</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN NEUROCIENCIA COGNITIVA APLICADA</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I478" t="n">
+        <v>84</v>
+      </c>
+      <c r="J478" t="n">
+        <v>7</v>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L478" t="n">
+        <v>2283968</v>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N478" s="2" t="n">
+        <v>44993</v>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>Psicología</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2810</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSIDAD DE LA COSTA CUC</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F479" t="n">
+        <v>106711</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN GESTION DE LAS TECNOLOGIAS DE LA INFORMACION Y LA COMUNICACION</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I479" t="n">
+        <v>42</v>
+      </c>
+      <c r="J479" t="n">
+        <v>4</v>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L479" t="n">
+        <v>972010</v>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N479" s="2" t="n">
+        <v>45827</v>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Duitama</t>
+        </is>
+      </c>
+      <c r="F480" t="n">
+        <v>118408</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CAMBIO CLIMÁTICO Y DESARROLLO SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I480" t="n">
+        <v>41</v>
+      </c>
+      <c r="J480" t="n">
+        <v>4</v>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N480" s="2" t="n">
+        <v>44421</v>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>Tecnología de protección del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA - ITM</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F481" t="n">
+        <v>101977</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN GESTIÓN DE LA INNOVACIÓN TECNOLÓGICA, COOPERACIÓN Y DESARROLLO REGIONAL</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I481" t="n">
+        <v>60</v>
+      </c>
+      <c r="J481" t="n">
+        <v>4</v>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L481" t="n">
+        <v>10381800</v>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N481" s="2" t="n">
+        <v>41172</v>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>22/09/2026</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V481"/>
+  <dimension ref="A1:V489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45920,10 +45920,8 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A462" t="n">
+        <v>1203</v>
       </c>
       <c r="B462" t="inlineStr">
         <is>
@@ -45975,7 +45973,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N462" s="2" t="n">
+      <c r="N462" s="1" t="n">
         <v>46184</v>
       </c>
       <c r="O462" t="inlineStr">
@@ -46020,10 +46018,8 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A463" t="n">
+        <v>1710</v>
       </c>
       <c r="B463" t="inlineStr">
         <is>
@@ -46075,7 +46071,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N463" s="2" t="n">
+      <c r="N463" s="1" t="n">
         <v>43189</v>
       </c>
       <c r="O463" t="inlineStr">
@@ -46120,10 +46116,8 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A464" t="n">
+        <v>1710</v>
       </c>
       <c r="B464" t="inlineStr">
         <is>
@@ -46175,7 +46169,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N464" s="2" t="n">
+      <c r="N464" s="1" t="n">
         <v>45420</v>
       </c>
       <c r="O464" t="inlineStr">
@@ -46220,10 +46214,8 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A465" t="n">
+        <v>1710</v>
       </c>
       <c r="B465" t="inlineStr">
         <is>
@@ -46275,7 +46267,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N465" s="2" t="n">
+      <c r="N465" s="1" t="n">
         <v>43189</v>
       </c>
       <c r="O465" t="inlineStr">
@@ -46320,10 +46312,8 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A466" t="n">
+        <v>1710</v>
       </c>
       <c r="B466" t="inlineStr">
         <is>
@@ -46375,7 +46365,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N466" s="2" t="n">
+      <c r="N466" s="1" t="n">
         <v>43228</v>
       </c>
       <c r="O466" t="inlineStr">
@@ -46420,10 +46410,8 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A467" t="n">
+        <v>1713</v>
       </c>
       <c r="B467" t="inlineStr">
         <is>
@@ -46475,7 +46463,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N467" s="2" t="n">
+      <c r="N467" s="1" t="n">
         <v>45146</v>
       </c>
       <c r="O467" t="inlineStr">
@@ -46520,10 +46508,8 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A468" t="n">
+        <v>1828</v>
       </c>
       <c r="B468" t="inlineStr">
         <is>
@@ -46575,7 +46561,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N468" s="2" t="n">
+      <c r="N468" s="1" t="n">
         <v>43095</v>
       </c>
       <c r="O468" t="inlineStr">
@@ -46620,10 +46606,8 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A469" t="n">
+        <v>1828</v>
       </c>
       <c r="B469" t="inlineStr">
         <is>
@@ -46675,7 +46659,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N469" s="2" t="n">
+      <c r="N469" s="1" t="n">
         <v>43270</v>
       </c>
       <c r="O469" t="inlineStr">
@@ -46720,10 +46704,8 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A470" t="n">
+        <v>1828</v>
       </c>
       <c r="B470" t="inlineStr">
         <is>
@@ -46775,7 +46757,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N470" s="2" t="n">
+      <c r="N470" s="1" t="n">
         <v>43327</v>
       </c>
       <c r="O470" t="inlineStr">
@@ -46820,10 +46802,8 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A471" t="n">
+        <v>1828</v>
       </c>
       <c r="B471" t="inlineStr">
         <is>
@@ -46875,7 +46855,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N471" s="2" t="n">
+      <c r="N471" s="1" t="n">
         <v>43532</v>
       </c>
       <c r="O471" t="inlineStr">
@@ -46920,10 +46900,8 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A472" t="n">
+        <v>1828</v>
       </c>
       <c r="B472" t="inlineStr">
         <is>
@@ -46975,7 +46953,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N472" s="2" t="n">
+      <c r="N472" s="1" t="n">
         <v>43488</v>
       </c>
       <c r="O472" t="inlineStr">
@@ -47020,10 +46998,8 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A473" t="n">
+        <v>1828</v>
       </c>
       <c r="B473" t="inlineStr">
         <is>
@@ -47077,7 +47053,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N473" s="2" t="n">
+      <c r="N473" s="1" t="n">
         <v>43326</v>
       </c>
       <c r="O473" t="inlineStr">
@@ -47122,10 +47098,8 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A474" t="n">
+        <v>2102</v>
       </c>
       <c r="B474" t="inlineStr">
         <is>
@@ -47179,7 +47153,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N474" s="2" t="n">
+      <c r="N474" s="1" t="n">
         <v>39308</v>
       </c>
       <c r="O474" t="inlineStr">
@@ -47224,10 +47198,8 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A475" t="n">
+        <v>2102</v>
       </c>
       <c r="B475" t="inlineStr">
         <is>
@@ -47281,7 +47253,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N475" s="2" t="n">
+      <c r="N475" s="1" t="n">
         <v>45182</v>
       </c>
       <c r="O475" t="inlineStr">
@@ -47326,10 +47298,8 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A476" t="n">
+        <v>2805</v>
       </c>
       <c r="B476" t="inlineStr">
         <is>
@@ -47383,7 +47353,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N476" s="2" t="n">
+      <c r="N476" s="1" t="n">
         <v>45355</v>
       </c>
       <c r="O476" t="inlineStr">
@@ -47428,10 +47398,8 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A477" t="n">
+        <v>2805</v>
       </c>
       <c r="B477" t="inlineStr">
         <is>
@@ -47485,7 +47453,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N477" s="2" t="n">
+      <c r="N477" s="1" t="n">
         <v>45037</v>
       </c>
       <c r="O477" t="inlineStr">
@@ -47530,10 +47498,8 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>2810</t>
-        </is>
+      <c r="A478" t="n">
+        <v>2810</v>
       </c>
       <c r="B478" t="inlineStr">
         <is>
@@ -47587,7 +47553,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N478" s="2" t="n">
+      <c r="N478" s="1" t="n">
         <v>44993</v>
       </c>
       <c r="O478" t="inlineStr">
@@ -47632,10 +47598,8 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>2810</t>
-        </is>
+      <c r="A479" t="n">
+        <v>2810</v>
       </c>
       <c r="B479" t="inlineStr">
         <is>
@@ -47689,7 +47653,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N479" s="2" t="n">
+      <c r="N479" s="1" t="n">
         <v>45827</v>
       </c>
       <c r="O479" t="inlineStr">
@@ -47734,10 +47698,8 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A480" t="n">
+        <v>2829</v>
       </c>
       <c r="B480" t="inlineStr">
         <is>
@@ -47789,7 +47751,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N480" s="2" t="n">
+      <c r="N480" s="1" t="n">
         <v>44421</v>
       </c>
       <c r="O480" t="inlineStr">
@@ -47834,10 +47796,8 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
+      <c r="A481" t="n">
+        <v>3302</v>
       </c>
       <c r="B481" t="inlineStr">
         <is>
@@ -47891,7 +47851,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N481" s="2" t="n">
+      <c r="N481" s="1" t="n">
         <v>41172</v>
       </c>
       <c r="O481" t="inlineStr">
@@ -47932,6 +47892,814 @@
       <c r="V481" t="inlineStr">
         <is>
           <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE BOGOTA - JORGE TADEO LOZANO</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F482" t="n">
+        <v>108230</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ESTÁNDARES INTERNACIONALES DE CONTABILIDAD Y AUDITORÍA</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I482" t="n">
+        <v>24</v>
+      </c>
+      <c r="J482" t="n">
+        <v>2</v>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N482" s="2" t="n">
+        <v>43592</v>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE BOGOTA - JORGE TADEO LOZANO</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F483" t="n">
+        <v>106885</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN FINANZAS CORPORATIVAS Y BANCA DE INVERSIÓN</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I483" t="n">
+        <v>24</v>
+      </c>
+      <c r="J483" t="n">
+        <v>2</v>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N483" s="2" t="n">
+        <v>43224</v>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>1707</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSIDAD DE BOGOTA - JORGE TADEO LOZANO</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F484" t="n">
+        <v>104975</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN PERIODISMO DIGITAL</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I484" t="n">
+        <v>24</v>
+      </c>
+      <c r="J484" t="n">
+        <v>3</v>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N484" s="2" t="n">
+        <v>42290</v>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F485" t="n">
+        <v>103848</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN INGENIERÍA ELÉCTRICA Y ELECTRÓNICA</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I485" t="n">
+        <v>120</v>
+      </c>
+      <c r="J485" t="n">
+        <v>8</v>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L485" t="n">
+        <v>21914626</v>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N485" s="2" t="n">
+        <v>44363</v>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>Electrónica y automatización</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F486" t="n">
+        <v>108977</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I486" t="n">
+        <v>40</v>
+      </c>
+      <c r="J486" t="n">
+        <v>3</v>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N486" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>Ingeniería y procesos químicos</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>Ingeniería química y afines</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F487" t="n">
+        <v>10673</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN EDUCACION SUPERIOR A DISTANCIA</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I487" t="n">
+        <v>24</v>
+      </c>
+      <c r="J487" t="n">
+        <v>2</v>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L487" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N487" s="2" t="n">
+        <v>36790</v>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F488" t="n">
+        <v>10675</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN PEDAGOGIA PARA EL DESARROLLO DEL APRENDIZAJE AUTONOMO</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I488" t="n">
+        <v>24</v>
+      </c>
+      <c r="J488" t="n">
+        <v>2</v>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L488" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N488" s="2" t="n">
+        <v>36790</v>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T488" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F489" t="n">
+        <v>107232</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN REDES DE NUEVA GENERACIÓN</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I489" t="n">
+        <v>24</v>
+      </c>
+      <c r="J489" t="n">
+        <v>2</v>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L489" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N489" s="2" t="n">
+        <v>43326</v>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T489" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V489"/>
+  <dimension ref="A1:V492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47896,10 +47896,8 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
+      <c r="A482" t="n">
+        <v>1707</v>
       </c>
       <c r="B482" t="inlineStr">
         <is>
@@ -47951,7 +47949,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N482" s="2" t="n">
+      <c r="N482" s="1" t="n">
         <v>43592</v>
       </c>
       <c r="O482" t="inlineStr">
@@ -47996,10 +47994,8 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
+      <c r="A483" t="n">
+        <v>1707</v>
       </c>
       <c r="B483" t="inlineStr">
         <is>
@@ -48051,7 +48047,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N483" s="2" t="n">
+      <c r="N483" s="1" t="n">
         <v>43224</v>
       </c>
       <c r="O483" t="inlineStr">
@@ -48096,10 +48092,8 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>1707</t>
-        </is>
+      <c r="A484" t="n">
+        <v>1707</v>
       </c>
       <c r="B484" t="inlineStr">
         <is>
@@ -48151,7 +48145,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N484" s="2" t="n">
+      <c r="N484" s="1" t="n">
         <v>42290</v>
       </c>
       <c r="O484" t="inlineStr">
@@ -48196,10 +48190,8 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A485" t="n">
+        <v>1713</v>
       </c>
       <c r="B485" t="inlineStr">
         <is>
@@ -48253,7 +48245,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N485" s="2" t="n">
+      <c r="N485" s="1" t="n">
         <v>44363</v>
       </c>
       <c r="O485" t="inlineStr">
@@ -48298,10 +48290,8 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="A486" t="n">
+        <v>1830</v>
       </c>
       <c r="B486" t="inlineStr">
         <is>
@@ -48353,7 +48343,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N486" s="2" t="n">
+      <c r="N486" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O486" t="inlineStr">
@@ -48398,10 +48388,8 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A487" t="n">
+        <v>2102</v>
       </c>
       <c r="B487" t="inlineStr">
         <is>
@@ -48455,7 +48443,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N487" s="2" t="n">
+      <c r="N487" s="1" t="n">
         <v>36790</v>
       </c>
       <c r="O487" t="inlineStr">
@@ -48500,10 +48488,8 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A488" t="n">
+        <v>2102</v>
       </c>
       <c r="B488" t="inlineStr">
         <is>
@@ -48557,7 +48543,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N488" s="2" t="n">
+      <c r="N488" s="1" t="n">
         <v>36790</v>
       </c>
       <c r="O488" t="inlineStr">
@@ -48602,10 +48588,8 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A489" t="n">
+        <v>2102</v>
       </c>
       <c r="B489" t="inlineStr">
         <is>
@@ -48659,7 +48643,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N489" s="2" t="n">
+      <c r="N489" s="1" t="n">
         <v>43326</v>
       </c>
       <c r="O489" t="inlineStr">
@@ -48700,6 +48684,308 @@
       <c r="V489" t="inlineStr">
         <is>
           <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>1117</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD MILITAR-NUEVA GRANADA</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F490" t="n">
+        <v>54911</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN INGENIERIA DE PAVIMENTOS</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I490" t="n">
+        <v>33</v>
+      </c>
+      <c r="J490" t="n">
+        <v>3</v>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>Sin definir</t>
+        </is>
+      </c>
+      <c r="N490" s="2" t="n">
+        <v>36847</v>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA SABANA</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>Chía</t>
+        </is>
+      </c>
+      <c r="F491" t="n">
+        <v>4376</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GERENCIA DEL SERVICIO</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I491" t="n">
+        <v>24</v>
+      </c>
+      <c r="J491" t="n">
+        <v>2</v>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L491" t="n">
+        <v>19436000</v>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N491" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EAN</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F492" t="n">
+        <v>52113</v>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN AUDITORIA Y GARANTIA DE CALIDAD EN SALUD CON ENFASIS EN EPIDEMIOLOGIA</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I492" t="n">
+        <v>26</v>
+      </c>
+      <c r="J492" t="n">
+        <v>2</v>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N492" s="2" t="n">
+        <v>43812</v>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V492"/>
+  <dimension ref="A1:V500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48688,10 +48688,8 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
+      <c r="A490" t="n">
+        <v>1117</v>
       </c>
       <c r="B490" t="inlineStr">
         <is>
@@ -48743,7 +48741,7 @@
           <t>Sin definir</t>
         </is>
       </c>
-      <c r="N490" s="2" t="n">
+      <c r="N490" s="1" t="n">
         <v>36847</v>
       </c>
       <c r="O490" t="inlineStr">
@@ -48788,10 +48786,8 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A491" t="n">
+        <v>1711</v>
       </c>
       <c r="B491" t="inlineStr">
         <is>
@@ -48845,7 +48841,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N491" s="2" t="n">
+      <c r="N491" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O491" t="inlineStr">
@@ -48890,10 +48886,8 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>2812</t>
-        </is>
+      <c r="A492" t="n">
+        <v>2812</v>
       </c>
       <c r="B492" t="inlineStr">
         <is>
@@ -48945,7 +48939,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N492" s="2" t="n">
+      <c r="N492" s="1" t="n">
         <v>43812</v>
       </c>
       <c r="O492" t="inlineStr">
@@ -48986,6 +48980,810 @@
       <c r="V492" t="inlineStr">
         <is>
           <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F493" t="n">
+        <v>104450</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DERECHO DEL PROCESO</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I493" t="n">
+        <v>30</v>
+      </c>
+      <c r="J493" t="n">
+        <v>2</v>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L493" t="n">
+        <v>6663945</v>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N493" s="2" t="n">
+        <v>42133</v>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F494" t="n">
+        <v>103719</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DIRECCION DE ORGANIZACIONES PRESTADORAS DE SERVICIOS DE SALUD</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I494" t="n">
+        <v>26</v>
+      </c>
+      <c r="J494" t="n">
+        <v>2</v>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N494" s="2" t="n">
+        <v>41898</v>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T494" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="U494" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V494" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F495" t="n">
+        <v>103718</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DIRECCION FINANCIERA</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I495" t="n">
+        <v>26</v>
+      </c>
+      <c r="J495" t="n">
+        <v>2</v>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N495" s="2" t="n">
+        <v>41898</v>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T495" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="U495" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V495" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F496" t="n">
+        <v>103757</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DIRECCIÓN PARA EL DESARROLLO DE LA GESTIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I496" t="n">
+        <v>26</v>
+      </c>
+      <c r="J496" t="n">
+        <v>2</v>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N496" s="2" t="n">
+        <v>41903</v>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T496" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="U496" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V496" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F497" t="n">
+        <v>103869</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GERENCIA DE LA CALIDAD Y AUDITORIA EN SERVICIOS DE SALUD</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I497" t="n">
+        <v>27</v>
+      </c>
+      <c r="J497" t="n">
+        <v>1</v>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N497" s="2" t="n">
+        <v>41974</v>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T497" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="U497" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V497" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F498" t="n">
+        <v>102911</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DEL TALENTO HUMANO</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I498" t="n">
+        <v>28</v>
+      </c>
+      <c r="J498" t="n">
+        <v>2</v>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L498" t="n">
+        <v>8217000</v>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N498" s="2" t="n">
+        <v>41606</v>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T498" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="U498" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V498" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F499" t="n">
+        <v>105362</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GESTIÓN AMBIENTAL EN LA INDUSTRIA MINERA Y PETROLERA</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I499" t="n">
+        <v>25</v>
+      </c>
+      <c r="J499" t="n">
+        <v>2</v>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N499" s="2" t="n">
+        <v>42418</v>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>Tecnología de protección del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T499" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="U499" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V499" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F500" t="n">
+        <v>105175</v>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN GESTIÓN DE CIENCIA, TECNOLOGÍA E INNOVACIÓN</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I500" t="n">
+        <v>49</v>
+      </c>
+      <c r="J500" t="n">
+        <v>4</v>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N500" s="2" t="n">
+        <v>42403</v>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T500" t="inlineStr">
+        <is>
+          <t>13/10/2026</t>
+        </is>
+      </c>
+      <c r="U500" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V500" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V500"/>
+  <dimension ref="A1:V506"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48984,10 +48984,8 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A493" t="n">
+        <v>1818</v>
       </c>
       <c r="B493" t="inlineStr">
         <is>
@@ -49041,7 +49039,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N493" s="2" t="n">
+      <c r="N493" s="1" t="n">
         <v>42133</v>
       </c>
       <c r="O493" t="inlineStr">
@@ -49086,10 +49084,8 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A494" t="n">
+        <v>2832</v>
       </c>
       <c r="B494" t="inlineStr">
         <is>
@@ -49141,7 +49137,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N494" s="2" t="n">
+      <c r="N494" s="1" t="n">
         <v>41898</v>
       </c>
       <c r="O494" t="inlineStr">
@@ -49186,10 +49182,8 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A495" t="n">
+        <v>2832</v>
       </c>
       <c r="B495" t="inlineStr">
         <is>
@@ -49241,7 +49235,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N495" s="2" t="n">
+      <c r="N495" s="1" t="n">
         <v>41898</v>
       </c>
       <c r="O495" t="inlineStr">
@@ -49286,10 +49280,8 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A496" t="n">
+        <v>2832</v>
       </c>
       <c r="B496" t="inlineStr">
         <is>
@@ -49341,7 +49333,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N496" s="2" t="n">
+      <c r="N496" s="1" t="n">
         <v>41903</v>
       </c>
       <c r="O496" t="inlineStr">
@@ -49386,10 +49378,8 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A497" t="n">
+        <v>2832</v>
       </c>
       <c r="B497" t="inlineStr">
         <is>
@@ -49441,7 +49431,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N497" s="2" t="n">
+      <c r="N497" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="O497" t="inlineStr">
@@ -49486,10 +49476,8 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A498" t="n">
+        <v>2832</v>
       </c>
       <c r="B498" t="inlineStr">
         <is>
@@ -49543,7 +49531,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N498" s="2" t="n">
+      <c r="N498" s="1" t="n">
         <v>41606</v>
       </c>
       <c r="O498" t="inlineStr">
@@ -49588,10 +49576,8 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A499" t="n">
+        <v>2832</v>
       </c>
       <c r="B499" t="inlineStr">
         <is>
@@ -49643,7 +49629,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N499" s="2" t="n">
+      <c r="N499" s="1" t="n">
         <v>42418</v>
       </c>
       <c r="O499" t="inlineStr">
@@ -49688,10 +49674,8 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A500" t="n">
+        <v>2832</v>
       </c>
       <c r="B500" t="inlineStr">
         <is>
@@ -49743,7 +49727,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N500" s="2" t="n">
+      <c r="N500" s="1" t="n">
         <v>42403</v>
       </c>
       <c r="O500" t="inlineStr">
@@ -49784,6 +49768,612 @@
       <c r="V500" t="inlineStr">
         <is>
           <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F501" t="n">
+        <v>109307</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN BIOTECNOLOGIA AGROAMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I501" t="n">
+        <v>25</v>
+      </c>
+      <c r="J501" t="n">
+        <v>2</v>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L501" t="n">
+        <v>5310000</v>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N501" s="2" t="n">
+        <v>44026</v>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>Producción agrícola y ganadera</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>Agronomía</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V501" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA MARIA CANO</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F502" t="n">
+        <v>107512</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN ATENCIÓN INTEGRAL A LA PRIMERA INFANCIA</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I502" t="n">
+        <v>26</v>
+      </c>
+      <c r="J502" t="n">
+        <v>2</v>
+      </c>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L502" t="n">
+        <v>7426696</v>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N502" s="2" t="n">
+        <v>43417</v>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>Salud no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V502" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA AGUSTINIANA- UNIAGUSTINIANA</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F503" t="n">
+        <v>55008</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GERENCIA DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I503" t="n">
+        <v>24</v>
+      </c>
+      <c r="J503" t="n">
+        <v>1</v>
+      </c>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N503" s="2" t="n">
+        <v>40148</v>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V503" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA AGUSTINIANA- UNIAGUSTINIANA</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F504" t="n">
+        <v>105127</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA ESTRATÉGICA DE MARKETING</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I504" t="n">
+        <v>26</v>
+      </c>
+      <c r="J504" t="n">
+        <v>2</v>
+      </c>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L504" t="n">
+        <v>5241000</v>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N504" s="2" t="n">
+        <v>42338</v>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V504" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA AGUSTINIANA- UNIAGUSTINIANA</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F505" t="n">
+        <v>54883</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GESTION AMBIENTAL</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I505" t="n">
+        <v>24</v>
+      </c>
+      <c r="J505" t="n">
+        <v>1</v>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N505" s="2" t="n">
+        <v>40081</v>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R505" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V505" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA AGUSTINIANA- UNIAGUSTINIANA</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F506" t="n">
+        <v>9759</v>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN SEGURIDAD SOCIAL INTEGRAL</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I506" t="n">
+        <v>24</v>
+      </c>
+      <c r="J506" t="n">
+        <v>3</v>
+      </c>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N506" s="2" t="n">
+        <v>36559</v>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>Servicios de seguridad</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>Servicios de seguridad no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R506" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V506" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V506"/>
+  <dimension ref="A1:V510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49772,10 +49772,8 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A501" t="n">
+        <v>2102</v>
       </c>
       <c r="B501" t="inlineStr">
         <is>
@@ -49829,7 +49827,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N501" s="2" t="n">
+      <c r="N501" s="1" t="n">
         <v>44026</v>
       </c>
       <c r="O501" t="inlineStr">
@@ -49874,10 +49872,8 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>2721</t>
-        </is>
+      <c r="A502" t="n">
+        <v>2721</v>
       </c>
       <c r="B502" t="inlineStr">
         <is>
@@ -49931,7 +49927,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N502" s="2" t="n">
+      <c r="N502" s="1" t="n">
         <v>43417</v>
       </c>
       <c r="O502" t="inlineStr">
@@ -49976,10 +49972,8 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
+      <c r="A503" t="n">
+        <v>2834</v>
       </c>
       <c r="B503" t="inlineStr">
         <is>
@@ -50031,7 +50025,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N503" s="2" t="n">
+      <c r="N503" s="1" t="n">
         <v>40148</v>
       </c>
       <c r="O503" t="inlineStr">
@@ -50076,10 +50070,8 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
+      <c r="A504" t="n">
+        <v>2834</v>
       </c>
       <c r="B504" t="inlineStr">
         <is>
@@ -50133,7 +50125,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N504" s="2" t="n">
+      <c r="N504" s="1" t="n">
         <v>42338</v>
       </c>
       <c r="O504" t="inlineStr">
@@ -50178,10 +50170,8 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
+      <c r="A505" t="n">
+        <v>2834</v>
       </c>
       <c r="B505" t="inlineStr">
         <is>
@@ -50233,7 +50223,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N505" s="2" t="n">
+      <c r="N505" s="1" t="n">
         <v>40081</v>
       </c>
       <c r="O505" t="inlineStr">
@@ -50278,10 +50268,8 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
+      <c r="A506" t="n">
+        <v>2834</v>
       </c>
       <c r="B506" t="inlineStr">
         <is>
@@ -50333,7 +50321,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N506" s="2" t="n">
+      <c r="N506" s="1" t="n">
         <v>36559</v>
       </c>
       <c r="O506" t="inlineStr">
@@ -50374,6 +50362,406 @@
       <c r="V506" t="inlineStr">
         <is>
           <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F507" t="n">
+        <v>105182</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN SANIDAD ANIMAL</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I507" t="n">
+        <v>28</v>
+      </c>
+      <c r="J507" t="n">
+        <v>2</v>
+      </c>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N507" s="2" t="n">
+        <v>42403</v>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>Veterinaria</t>
+        </is>
+      </c>
+      <c r="R507" t="inlineStr">
+        <is>
+          <t>Medicina veterinaria</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V507" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>FUNDACION DE EDUCACION SUPERIOR SAN JOSE -FESSANJOSE-</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="F508" t="n">
+        <v>104883</v>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION TECNOLOGICA EN CALIDAD Y SERVICIO DE PRODUCTOS AGROINDUSTRIALES</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I508" t="n">
+        <v>24</v>
+      </c>
+      <c r="J508" t="n">
+        <v>2</v>
+      </c>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N508" s="2" t="n">
+        <v>42253</v>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarias relativos a agropecuario, silvicultura, pesca y veterinaria</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarias relativos a agropecuario, silvicultura, pesca y veterinaria</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t>Ingeniería agrícola, forestal y afines</t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>Especialización tecnológica</t>
+        </is>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V508" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>FUNDACION DE EDUCACION SUPERIOR SAN JOSE -FESSANJOSE-</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="F509" t="n">
+        <v>104778</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION TECNOLOGICA EN GESTION AMBIENTAL SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I509" t="n">
+        <v>24</v>
+      </c>
+      <c r="J509" t="n">
+        <v>2</v>
+      </c>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N509" s="2" t="n">
+        <v>42211</v>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>Tecnología de protección del medio ambiente</t>
+        </is>
+      </c>
+      <c r="R509" t="inlineStr">
+        <is>
+          <t>Ingeniería ambiental, sanitaria y afines</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>Especialización tecnológica</t>
+        </is>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V509" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>4702</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>FUNDACION DE EDUCACION SUPERIOR SAN JOSE -FESSANJOSE-</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>El Bagre</t>
+        </is>
+      </c>
+      <c r="F510" t="n">
+        <v>104777</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION TECNOLOGICA EN GESTION DE MINERIA AMBIENTALMENTE SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I510" t="n">
+        <v>24</v>
+      </c>
+      <c r="J510" t="n">
+        <v>2</v>
+      </c>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N510" s="2" t="n">
+        <v>42211</v>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>Industria y procesamiento</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>Minería y extracción</t>
+        </is>
+      </c>
+      <c r="R510" t="inlineStr">
+        <is>
+          <t>Ingeniería de minas, metalurgia y afines</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>Especialización tecnológica</t>
+        </is>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V510" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V510"/>
+  <dimension ref="A1:V512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -50366,10 +50366,8 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A507" t="n">
+        <v>2832</v>
       </c>
       <c r="B507" t="inlineStr">
         <is>
@@ -50421,7 +50419,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N507" s="2" t="n">
+      <c r="N507" s="1" t="n">
         <v>42403</v>
       </c>
       <c r="O507" t="inlineStr">
@@ -50466,10 +50464,8 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>4702</t>
-        </is>
+      <c r="A508" t="n">
+        <v>4702</v>
       </c>
       <c r="B508" t="inlineStr">
         <is>
@@ -50521,7 +50517,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N508" s="2" t="n">
+      <c r="N508" s="1" t="n">
         <v>42253</v>
       </c>
       <c r="O508" t="inlineStr">
@@ -50566,10 +50562,8 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>4702</t>
-        </is>
+      <c r="A509" t="n">
+        <v>4702</v>
       </c>
       <c r="B509" t="inlineStr">
         <is>
@@ -50621,7 +50615,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N509" s="2" t="n">
+      <c r="N509" s="1" t="n">
         <v>42211</v>
       </c>
       <c r="O509" t="inlineStr">
@@ -50666,10 +50660,8 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>4702</t>
-        </is>
+      <c r="A510" t="n">
+        <v>4702</v>
       </c>
       <c r="B510" t="inlineStr">
         <is>
@@ -50721,7 +50713,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N510" s="2" t="n">
+      <c r="N510" s="1" t="n">
         <v>42211</v>
       </c>
       <c r="O510" t="inlineStr">
@@ -50760,6 +50752,208 @@
         </is>
       </c>
       <c r="V510" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD TECNOLOGICA DE PEREIRA - UTP</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="F511" t="n">
+        <v>115859</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN INVESTIGACION OPERATIVA Y ESTADISTICA</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I511" t="n">
+        <v>54</v>
+      </c>
+      <c r="J511" t="n">
+        <v>4</v>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N511" s="2" t="n">
+        <v>44454</v>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>Estadística</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V511" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>1719</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CATOLICA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F512" t="n">
+        <v>104772</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN SEGURIDAD DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I512" t="n">
+        <v>26</v>
+      </c>
+      <c r="J512" t="n">
+        <v>2</v>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L512" t="n">
+        <v>8585000</v>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N512" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>Diseño y administración de redes y bases de datos</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V512" t="inlineStr">
         <is>
           <t>Ingenierías</t>
         </is>
